--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="489">
   <si>
     <t>Filename</t>
   </si>
@@ -811,673 +811,676 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9986,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.0017,0.0005,0.0000,0.9991</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9950,0.0003,0.0000,0.0029</t>
+  </si>
+  <si>
+    <t>0.0358,0.0022,0.0001,0.9774</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9243,0.0011,0.0586,0.0002</t>
-  </si>
-  <si>
-    <t>0.0226,0.0128,0.9452,0.0006</t>
-  </si>
-  <si>
-    <t>0.0783,0.0026,0.9595,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.0020,0.9966,0.0001</t>
-  </si>
-  <si>
-    <t>0.9944,0.0003,0.0011,0.0001</t>
+    <t>0.9990,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9820,0.0014,0.0055,0.0001</t>
+  </si>
+  <si>
+    <t>0.3717,0.0007,0.6258,0.0007</t>
+  </si>
+  <si>
+    <t>0.0710,0.0002,0.9642,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0006,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.9925,0.0007,0.0017,0.0002</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.9992,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.2085,0.8173,0.0040,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9994,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.7750,0.0010,0.1908,0.0012</t>
-  </si>
-  <si>
-    <t>0.2813,0.0012,0.7085,0.0014</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9990,0.0009</t>
-  </si>
-  <si>
-    <t>0.0036,0.0021,0.9913,0.0008</t>
-  </si>
-  <si>
-    <t>0.1430,0.0000,0.9206,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9985,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9992,0.0006</t>
-  </si>
-  <si>
-    <t>0.0193,0.9760,0.0017,0.0070</t>
-  </si>
-  <si>
-    <t>0.9818,0.0077,0.0031,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9997,0.0021</t>
-  </si>
-  <si>
-    <t>0.0009,0.9952,0.0154,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.6978,0.0038,0.1810,0.0004</t>
-  </si>
-  <si>
-    <t>0.0283,0.9749,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0090,0.9793,0.0189,0.0005</t>
-  </si>
-  <si>
-    <t>0.0029,0.1474,0.8832,0.0036</t>
-  </si>
-  <si>
-    <t>0.0196,0.0009,0.9807,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.0019,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.0393,0.0005,0.9566,0.0012</t>
-  </si>
-  <si>
-    <t>0.0047,0.0265,0.9895,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.9953,0.0088,0.0003</t>
+    <t>0.0002,0.9995,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0771,0.9406,0.0052,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9623,0.0008,0.0222,0.0004</t>
+  </si>
+  <si>
+    <t>0.0537,0.0087,0.9043,0.0028</t>
+  </si>
+  <si>
+    <t>0.0026,0.0004,0.9949,0.0008</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.1075,0.0004,0.9131,0.0003</t>
+  </si>
+  <si>
+    <t>0.0087,0.0010,0.9873,0.0018</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0054,0.9927,0.0005,0.0027</t>
+  </si>
+  <si>
+    <t>0.9924,0.0044,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9995,0.0011</t>
+  </si>
+  <si>
+    <t>0.0014,0.9960,0.0038,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0011,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9702,0.0008,0.0161,0.0002</t>
+  </si>
+  <si>
+    <t>0.8053,0.2011,0.0034,0.0019</t>
+  </si>
+  <si>
+    <t>0.0007,0.9969,0.0118,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.0071,0.9927,0.0008</t>
+  </si>
+  <si>
+    <t>0.0019,0.0008,0.9928,0.0023</t>
+  </si>
+  <si>
+    <t>0.0071,0.0073,0.9804,0.0012</t>
+  </si>
+  <si>
+    <t>0.0331,0.0006,0.9728,0.0008</t>
+  </si>
+  <si>
+    <t>0.0030,0.2120,0.9872,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.9804,0.0132,0.0021</t>
+  </si>
+  <si>
+    <t>0.0005,0.0013,0.9980,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9694,0.0004,0.9744</t>
+  </si>
+  <si>
+    <t>0.0011,0.9929,0.0013,0.0092</t>
+  </si>
+  <si>
+    <t>0.0001,0.9984,0.0163,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9973,0.0063,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0138,0.9966,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0005,0.9959,0.0015</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9998,0.0002</t>
   </si>
   <si>
-    <t>0.0001,0.9316,0.0003,0.9859</t>
-  </si>
-  <si>
-    <t>0.0013,0.9949,0.0033,0.0032</t>
-  </si>
-  <si>
-    <t>0.0001,0.9991,0.0045,0.0000</t>
+    <t>0.0001,0.0004,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0115,0.9964,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0014,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9301,0.0228,0.0109,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0073,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0013,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9656,0.8783,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0046,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0011,0.9950,0.0021</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9989,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9897,0.0009,0.0037,0.0002</t>
+  </si>
+  <si>
+    <t>0.0625,0.0006,0.9527,0.0015</t>
+  </si>
+  <si>
+    <t>0.0008,0.0050,0.9967,0.0085</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9520,0.8242,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.0474,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.9806,0.0000</t>
+  </si>
+  <si>
+    <t>0.0155,0.0002,0.0035,0.9872</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0014,0.0001,0.0025,0.9978</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0039,0.9989</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9990,0.0154,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9880,0.9854,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.8501,0.7788,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.8523,0.9443,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.9396,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9955,0.0636,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0043,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0029,0.0041,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.0073,0.0025,0.9940,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0001,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.9966,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0122,0.9903,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.9953,0.0019,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0002,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.2413,0.9769,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0017,0.9976,0.0011</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0055,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0027,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0010,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0024,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0052,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
+    <t>0.0001,0.9996,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0157,0.9845,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.7357,0.0132,0.1381,0.0029</t>
+  </si>
+  <si>
+    <t>0.9837,0.0019,0.0050,0.0002</t>
+  </si>
+  <si>
+    <t>0.0938,0.0244,0.6214,0.0080</t>
+  </si>
+  <si>
+    <t>0.0228,0.0059,0.9505,0.0052</t>
+  </si>
+  <si>
+    <t>0.0050,0.5003,0.0002,0.8626</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.9920,0.4944,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.1614,0.8667,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.6549,0.4012,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0029,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0112,0.9965,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.8611,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0163,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.0003,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2715,0.0031,0.6319,0.0018</t>
+  </si>
+  <si>
+    <t>0.0092,0.0001,0.9951,0.0001</t>
+  </si>
+  <si>
+    <t>0.9487,0.0031,0.0233,0.0007</t>
+  </si>
+  <si>
+    <t>0.1393,0.0014,0.0005,0.9420</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9965,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0203,0.9791,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0403,0.9688,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8463,0.0006,0.0009,0.1298</t>
+  </si>
+  <si>
+    <t>0.0003,0.0291,0.9983,0.0008</t>
+  </si>
+  <si>
+    <t>0.9979,0.0000,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.1641,0.7883,0.0142,0.0022</t>
+  </si>
+  <si>
+    <t>0.9980,0.0014,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9921,0.0046,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0661,0.9299,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9485,0.0281,0.0020,0.0015</t>
+  </si>
+  <si>
+    <t>0.9989,0.0008,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.3233,0.7598,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.4226,0.6209,0.0068,0.0002</t>
+  </si>
+  <si>
+    <t>0.2393,0.8539,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.4896,0.5681,0.0165,0.0015</t>
+  </si>
+  <si>
+    <t>0.9971,0.0036,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9956,0.0034,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.6961,0.3556,0.0072,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0635,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0006,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0060,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0052,0.0001,0.9966,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0058,0.9973,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0056,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0020,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0176,0.0008,0.9757,0.0013</t>
+  </si>
+  <si>
+    <t>0.0097,0.0033,0.9904,0.0003</t>
+  </si>
+  <si>
+    <t>0.0195,0.0022,0.9734,0.0014</t>
+  </si>
+  <si>
+    <t>0.0097,0.0158,0.9804,0.0003</t>
+  </si>
+  <si>
+    <t>0.0060,0.1180,0.8715,0.0006</t>
+  </si>
+  <si>
+    <t>0.8476,0.0016,0.1255,0.0003</t>
+  </si>
+  <si>
+    <t>0.9712,0.0087,0.0041,0.0010</t>
+  </si>
+  <si>
+    <t>0.0836,0.0014,0.9556,0.0003</t>
+  </si>
+  <si>
+    <t>0.1732,0.9024,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0390,0.9774,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.6875,0.4723,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8592,0.2386,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2012,0.8883,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4789,0.0348,0.3321,0.0003</t>
+  </si>
+  <si>
+    <t>0.9563,0.0005,0.0401,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9151,0.0134,0.0192,0.0017</t>
+  </si>
+  <si>
+    <t>0.9717,0.0026,0.0100,0.0004</t>
+  </si>
+  <si>
+    <t>0.0029,0.0045,0.9925,0.0024</t>
+  </si>
+  <si>
+    <t>0.0024,0.0295,0.9751,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.1718,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9979,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0084,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0008,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9718,0.0351,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0010,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0186,0.9963,0.0003</t>
+  </si>
+  <si>
+    <t>0.0237,0.0219,0.9269,0.0021</t>
+  </si>
+  <si>
+    <t>0.8717,0.0011,0.0777,0.0009</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0009,0.9985,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.0502,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0035,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.0020,0.9854,0.0010</t>
+  </si>
+  <si>
+    <t>0.0016,0.0012,0.9955,0.0010</t>
+  </si>
+  <si>
+    <t>0.9964,0.0002,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.7549,0.0003,0.3445,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0004,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0013,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9992,0.0008,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9938,0.5486,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0089,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0258,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9985,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9951,0.0001,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.1723,0.0006,0.8806,0.0007</t>
-  </si>
-  <si>
-    <t>0.0046,0.0060,0.9869,0.0065</t>
-  </si>
-  <si>
-    <t>0.0000,0.9966,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.8097,0.9059,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.4324,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9971,0.8888,0.0000</t>
-  </si>
-  <si>
-    <t>0.0777,0.0014,0.0108,0.9260</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.0005,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0027,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.7284,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9938,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.7262,0.9702,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0747,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.9807,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9958,0.5744,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0043,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9926,0.0134,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.0004,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0103,0.0140,0.9879,0.0002</t>
-  </si>
-  <si>
-    <t>0.8855,0.0100,0.0364,0.0103</t>
-  </si>
-  <si>
-    <t>0.0063,0.0002,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9986,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0064,0.9932,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9982,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4584,0.6266,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.7682,0.1002,0.0280,0.0007</t>
-  </si>
-  <si>
-    <t>0.6860,0.0009,0.2839,0.0005</t>
-  </si>
-  <si>
-    <t>0.2049,0.0860,0.2424,0.0044</t>
-  </si>
-  <si>
-    <t>0.0366,0.0104,0.8954,0.0052</t>
-  </si>
-  <si>
-    <t>0.0032,0.8706,0.0162,0.6312</t>
-  </si>
-  <si>
-    <t>0.0008,0.9984,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0022</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9934,0.9382,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7926,0.2456,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.7898,0.2334,0.0050,0.0010</t>
-  </si>
-  <si>
-    <t>0.9963,0.0025,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.4915,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9230,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0033,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0112,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.9958,0.0002,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.7217,0.0055,0.1424,0.0036</t>
-  </si>
-  <si>
-    <t>0.0238,0.0000,0.9895,0.0001</t>
-  </si>
-  <si>
-    <t>0.8733,0.0059,0.0841,0.0035</t>
-  </si>
-  <si>
-    <t>0.0220,0.0014,0.0000,0.9934</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9930,0.9908,0.0000</t>
-  </si>
-  <si>
-    <t>0.0584,0.9451,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0340,0.9676,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0626,0.0006,0.0047,0.9602</t>
-  </si>
-  <si>
-    <t>0.0017,0.0079,0.9965,0.0007</t>
-  </si>
-  <si>
-    <t>0.9262,0.0000,0.0009,0.0362</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.4905,0.3630,0.0215,0.0025</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0007,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0881,0.9057,0.0018,0.0016</t>
-  </si>
-  <si>
-    <t>0.3738,0.5131,0.0124,0.0054</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9890,0.0145,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.8289,0.2188,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.4472,0.6781,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9877,0.0132,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9939,0.0080,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0037,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7625,0.2051,0.0454,0.0022</t>
-  </si>
-  <si>
-    <t>0.0001,0.0046,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9106,0.0453,0.0313,0.0028</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0326,0.9977,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0042,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0263,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0029,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0375,0.0023,0.9558,0.0010</t>
-  </si>
-  <si>
-    <t>0.0195,0.0006,0.9874,0.0002</t>
-  </si>
-  <si>
-    <t>0.0073,0.0010,0.9897,0.0008</t>
-  </si>
-  <si>
-    <t>0.0380,0.0033,0.9598,0.0008</t>
-  </si>
-  <si>
-    <t>0.0258,0.0067,0.9396,0.0006</t>
-  </si>
-  <si>
-    <t>0.3814,0.0021,0.5871,0.0008</t>
-  </si>
-  <si>
-    <t>0.9438,0.0098,0.0101,0.0019</t>
-  </si>
-  <si>
-    <t>0.1381,0.0044,0.8829,0.0014</t>
-  </si>
-  <si>
-    <t>0.0689,0.9578,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.9987,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9935,0.0108,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0046,0.9956,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0407,0.9759,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9438,0.0114,0.0145,0.0009</t>
-  </si>
-  <si>
-    <t>0.9876,0.0006,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.9944,0.0006,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.8723,0.0158,0.0546,0.0026</t>
-  </si>
-  <si>
-    <t>0.9732,0.0051,0.0057,0.0013</t>
-  </si>
-  <si>
-    <t>0.0049,0.0014,0.9851,0.0102</t>
-  </si>
-  <si>
-    <t>0.0030,0.0047,0.9895,0.0005</t>
-  </si>
-  <si>
-    <t>0.0029,0.0479,0.9788,0.0012</t>
-  </si>
-  <si>
-    <t>0.0010,0.0011,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.9542,0.5064,0.0001</t>
+    <t>0.9994,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0016,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9994,0.0004,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9988,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9919,0.0097,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0210,0.9981,0.0003</t>
-  </si>
-  <si>
-    <t>0.0106,0.6901,0.6483,0.0004</t>
-  </si>
-  <si>
-    <t>0.9204,0.0052,0.0371,0.0007</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0013,0.9994,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0171,0.9965,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.0008,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0003,0.9979,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0005,0.9971,0.0010</t>
-  </si>
-  <si>
-    <t>0.0034,0.0019,0.9893,0.0036</t>
-  </si>
-  <si>
-    <t>0.7939,0.0019,0.1609,0.0016</t>
-  </si>
-  <si>
-    <t>0.3610,0.0001,0.7744,0.0003</t>
-  </si>
-  <si>
-    <t>0.9977,0.0001,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0028,0.9937,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0152,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.0259,0.9701,0.0011</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0053,0.0014,0.9904,0.0044</t>
-  </si>
-  <si>
-    <t>0.0137,0.0029,0.9814,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9957,0.0029</t>
-  </si>
-  <si>
-    <t>0.8620,0.0005,0.0015,0.1093</t>
-  </si>
-  <si>
-    <t>0.0905,0.0149,0.0000,0.9025</t>
-  </si>
-  <si>
-    <t>0.0025,0.0006,0.0000,0.9989</t>
-  </si>
-  <si>
-    <t>0.9583,0.0010,0.0001,0.0397</t>
+    <t>0.0042,0.2874,0.9092,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.1374,0.9932,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0446,0.9876,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0894,0.0005,0.9116,0.0023</t>
+  </si>
+  <si>
+    <t>0.0261,0.0087,0.9392,0.0020</t>
+  </si>
+  <si>
+    <t>0.0007,0.0017,0.9964,0.0008</t>
+  </si>
+  <si>
+    <t>0.9838,0.0006,0.0018,0.0045</t>
+  </si>
+  <si>
+    <t>0.0024,0.1014,0.0000,0.9948</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0001,0.0009</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1866,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1877,7 +1880,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1891,7 +1894,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1905,7 +1908,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1919,7 +1922,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1933,7 +1936,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1947,7 +1950,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1961,7 +1964,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1975,7 +1978,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1989,7 +1992,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2003,7 +2006,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2017,7 +2020,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2031,7 +2034,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2045,7 +2048,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2059,7 +2062,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2073,7 +2076,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2087,7 +2090,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2101,7 +2104,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2115,7 +2118,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2129,7 +2132,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2143,7 +2146,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2157,7 +2160,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2171,7 +2174,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2185,7 +2188,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2199,7 +2202,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2213,7 +2216,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2227,7 +2230,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2241,7 +2244,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2255,7 +2258,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2269,7 +2272,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2283,7 +2286,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2297,7 +2300,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2311,7 +2314,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2325,7 +2328,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2339,7 +2342,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2350,10 +2353,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2367,7 +2370,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2381,7 +2384,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2395,7 +2398,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2409,7 +2412,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2423,7 +2426,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2437,7 +2440,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2451,7 +2454,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2465,7 +2468,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2479,7 +2482,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2493,7 +2496,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2507,7 +2510,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2521,7 +2524,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2535,7 +2538,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2549,7 +2552,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2563,7 +2566,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2577,7 +2580,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2591,7 +2594,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2605,7 +2608,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2619,7 +2622,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2633,7 +2636,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2647,7 +2650,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2661,7 +2664,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2675,7 +2678,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2689,7 +2692,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2703,7 +2706,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2717,7 +2720,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2731,7 +2734,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2745,7 +2748,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2759,7 +2762,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2773,7 +2776,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2787,7 +2790,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2801,7 +2804,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2815,7 +2818,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2829,7 +2832,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2843,7 +2846,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2857,7 +2860,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2871,7 +2874,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2885,7 +2888,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2899,7 +2902,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2913,7 +2916,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2927,7 +2930,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2941,7 +2944,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2955,7 +2958,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2969,7 +2972,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2983,7 +2986,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2994,10 +2997,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3011,7 +3014,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3025,7 +3028,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3036,10 +3039,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3053,7 +3056,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3064,10 +3067,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3081,7 +3084,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3095,7 +3098,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3109,7 +3112,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3123,7 +3126,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3151,7 +3154,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>271</v>
+        <v>351</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3165,7 +3168,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>272</v>
+        <v>349</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3179,7 +3182,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3193,7 +3196,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3207,7 +3210,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3221,7 +3224,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3235,7 +3238,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3249,7 +3252,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>352</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3263,7 +3266,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>272</v>
+        <v>353</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3277,7 +3280,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>269</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3291,7 +3294,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3305,7 +3308,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3319,7 +3322,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3333,7 +3336,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3347,7 +3350,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3361,7 +3364,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3375,7 +3378,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3389,7 +3392,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3403,7 +3406,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3417,7 +3420,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3431,7 +3434,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3445,7 +3448,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3459,7 +3462,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3473,7 +3476,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3484,10 +3487,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3501,7 +3504,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3515,7 +3518,7 @@
         <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3529,7 +3532,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3543,7 +3546,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3557,7 +3560,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3568,10 +3571,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3585,7 +3588,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3596,10 +3599,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3613,7 +3616,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3627,7 +3630,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3641,7 +3644,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>270</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3655,7 +3658,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3669,7 +3672,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>269</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3683,7 +3686,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3697,7 +3700,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3711,7 +3714,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3739,7 +3742,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3753,7 +3756,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3767,7 +3770,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3781,7 +3784,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3795,7 +3798,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3806,10 +3809,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3823,7 +3826,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3837,7 +3840,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3851,7 +3854,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3865,7 +3868,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3879,7 +3882,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3893,7 +3896,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3907,7 +3910,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3921,7 +3924,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3935,7 +3938,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3949,7 +3952,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3963,7 +3966,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3977,7 +3980,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3988,10 +3991,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4005,7 +4008,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4019,7 +4022,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4033,7 +4036,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4047,7 +4050,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4058,10 +4061,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4075,7 +4078,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4089,7 +4092,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4103,7 +4106,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4114,10 +4117,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4131,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4145,7 +4148,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4159,7 +4162,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4173,7 +4176,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4187,7 +4190,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>394</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4201,7 +4204,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4215,7 +4218,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4229,7 +4232,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4243,7 +4246,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4254,10 +4257,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4268,10 +4271,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4285,7 +4288,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4296,10 +4299,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4313,7 +4316,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4327,7 +4330,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4341,7 +4344,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4355,7 +4358,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4369,7 +4372,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4383,7 +4386,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4397,7 +4400,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4411,7 +4414,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4425,7 +4428,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4439,7 +4442,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4453,7 +4456,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4467,7 +4470,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4481,7 +4484,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4495,7 +4498,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4509,7 +4512,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4523,7 +4526,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4537,7 +4540,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4551,7 +4554,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4562,10 +4565,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4579,7 +4582,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4593,7 +4596,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4607,7 +4610,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4621,7 +4624,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4635,7 +4638,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4646,10 +4649,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4663,7 +4666,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4674,10 +4677,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D203" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4691,7 +4694,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4705,7 +4708,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4719,7 +4722,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4733,7 +4736,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4747,7 +4750,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4761,7 +4764,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4775,7 +4778,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4789,7 +4792,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4800,10 +4803,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4817,7 +4820,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4831,7 +4834,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>378</v>
+        <v>452</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4845,7 +4848,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4859,7 +4862,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4873,7 +4876,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4887,7 +4890,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4901,7 +4904,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4915,7 +4918,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>455</v>
+        <v>410</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4929,7 +4932,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4940,10 +4943,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4957,7 +4960,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4971,7 +4974,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4985,7 +4988,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4999,7 +5002,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5013,7 +5016,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5027,7 +5030,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5041,7 +5044,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5055,7 +5058,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5069,7 +5072,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5083,7 +5086,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5094,10 +5097,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5111,7 +5114,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5125,7 +5128,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5139,7 +5142,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>471</v>
+        <v>354</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5167,7 +5170,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5181,7 +5184,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5195,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>473</v>
+        <v>349</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5209,7 +5212,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5223,7 +5226,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5237,7 +5240,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5251,7 +5254,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5265,7 +5268,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5279,7 +5282,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5293,7 +5296,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5307,7 +5310,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5321,7 +5324,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5335,7 +5338,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5349,7 +5352,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5363,7 +5366,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5377,7 +5380,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5391,7 +5394,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5405,7 +5408,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5419,7 +5422,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
